--- a/_business-operations/sales-forecast/26年yousky独立站目标销量计划.xlsx
+++ b/_business-operations/sales-forecast/26年yousky独立站目标销量计划.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qisanjiudekeaiduo/Downloads/python3/Harlottecc/inventory management plan/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qisanjiudekeaiduo/Downloads/python3/Harlottecc/_business-operations/sales-forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B67711B-00B2-A945-B232-74379B8C1A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA94A499-FC7F-7647-AC44-E4B5F1A97111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2160" windowWidth="24980" windowHeight="16960" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="1" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="销额销量预估" sheetId="1" r:id="rId1"/>
@@ -561,7 +561,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1"/>
@@ -569,7 +569,7 @@
     <col min="3" max="4" width="10" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" customHeight="1">
+    <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -583,7 +583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1">
+    <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -597,7 +597,7 @@
         <v>284978</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1">
+    <row r="3" spans="1:5" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -610,8 +610,12 @@
       <c r="D3" s="2">
         <v>2100</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="16.5" customHeight="1">
+      <c r="E3">
+        <f>SUM(B3:D3)</f>
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -628,7 +632,7 @@
         <v>135.70380952380953</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5" customHeight="1">
+    <row r="5" spans="1:5" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -645,7 +649,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.5" customHeight="1">
+    <row r="6" spans="1:5" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -768,7 +772,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4">
         <v>100</v>
@@ -778,7 +782,7 @@
       </c>
       <c r="F4" s="7">
         <f t="shared" si="0"/>
-        <v>3.3333333333333335</v>
+        <v>0</v>
       </c>
       <c r="G4" s="7">
         <f t="shared" si="1"/>
@@ -930,7 +934,7 @@
       </c>
       <c r="C13" s="10">
         <f>C4*$A$4</f>
-        <v>14999</v>
+        <v>0</v>
       </c>
       <c r="D13" s="10">
         <f>D4*$A$4</f>
@@ -998,7 +1002,7 @@
       </c>
       <c r="C17" s="10">
         <f>SUM(C11:C16)</f>
-        <v>106791.8</v>
+        <v>91792.8</v>
       </c>
       <c r="D17" s="10">
         <f>SUM(D11:D16)</f>

--- a/_business-operations/sales-forecast/26年yousky独立站目标销量计划.xlsx
+++ b/_business-operations/sales-forecast/26年yousky独立站目标销量计划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qisanjiudekeaiduo/Downloads/python3/Harlottecc/_business-operations/sales-forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA94A499-FC7F-7647-AC44-E4B5F1A97111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4838667D-AA96-0D40-B4E7-9964A7DBEE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="1" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
@@ -602,7 +602,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="C3" s="2">
         <v>1700</v>
@@ -612,7 +612,7 @@
       </c>
       <c r="E3">
         <f>SUM(B3:D3)</f>
-        <v>4600</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" customHeight="1">
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" s="10">
         <f>B2/B3</f>
-        <v>133.48975000000002</v>
+        <v>152.55971428571428</v>
       </c>
       <c r="C4" s="10">
         <f>C2/C3</f>
@@ -638,7 +638,7 @@
       </c>
       <c r="B5" s="7">
         <f>B3/B6</f>
-        <v>32000</v>
+        <v>28000</v>
       </c>
       <c r="C5" s="7">
         <f>C3/C6</f>
@@ -880,6 +880,12 @@
         <v>6.4516129032258061</v>
       </c>
     </row>
+    <row r="8" spans="1:8" ht="16.5" customHeight="1">
+      <c r="C8">
+        <f>SUM(C2:C7)</f>
+        <v>700</v>
+      </c>
+    </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1">
       <c r="B10" s="8" t="s">
         <v>20</v>
